--- a/order_generation/PO_excel/2EC-Pink.xlsx
+++ b/order_generation/PO_excel/2EC-Pink.xlsx
@@ -2055,9 +2055,9 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>

--- a/order_generation/PO_excel/2EC-Pink.xlsx
+++ b/order_generation/PO_excel/2EC-Pink.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -254,13 +254,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +761,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -766,7 +769,7 @@
 sales@hair-brushes.com    lucky@jsiu.com</t>
         </is>
       </c>
-      <c r="H1" s="28" t="n"/>
+      <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -892,48 +895,48 @@
       <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>2EC-Pink</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>细针洗头刷TPEE，硬度55，注意控制针头毛边，顶部印白色logo，颜色699C粉色，一盒两只</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="29" t="n">
         <v>3.5</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1018,7 +1021,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2031年04月26日</t>
+          <t>2025年11月23日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>

--- a/order_generation/PO_excel/2EC-Pink.xlsx
+++ b/order_generation/PO_excel/2EC-Pink.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年10月09日</t>
+          <t>2025年10月22日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月23日</t>
+          <t>2025年12月06日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>

--- a/order_generation/PO_excel/2EC-Pink.xlsx
+++ b/order_generation/PO_excel/2EC-Pink.xlsx
@@ -364,6 +364,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -389,6 +392,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -746,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -1021,7 +1027,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年12月06日</t>
+          <t>45天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1282,16 +1288,9 @@
     <row r="34" ht="21" customFormat="1" customHeight="1" s="6">
       <c r="H34" s="14" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="H38" s="14" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="12" t="n"/>
@@ -1392,7 +1391,6 @@
       <c r="A67" s="10" t="n"/>
       <c r="B67" s="12" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
@@ -1424,26 +1422,9 @@
       </c>
       <c r="F70" s="13" t="n"/>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="H80" s="14" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>

--- a/order_generation/PO_excel/2EC-Pink.xlsx
+++ b/order_generation/PO_excel/2EC-Pink.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2730" windowWidth="21540" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修改" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Arial"/>
       <charset val="134"/>
@@ -37,28 +37,16 @@
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="22"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
       <sz val="12"/>
     </font>
     <font>
@@ -87,38 +75,12 @@
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
       <family val="2"/>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="20"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -132,6 +94,33 @@
       <charset val="134"/>
       <family val="3"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -184,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,34 +194,34 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,25 +233,29 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +346,7 @@
     <ext cx="371475" cy="571500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -363,7 +356,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -381,7 +376,7 @@
     <ext cx="1266825" cy="1266825"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -391,7 +386,9 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -755,19 +752,20 @@
   <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
-    <col width="44.5703125" customWidth="1" style="7" min="2" max="2"/>
-    <col width="35.85546875" customWidth="1" style="7" min="3" max="3"/>
-    <col width="11.7109375" customWidth="1" style="7" min="4" max="4"/>
-    <col width="9.42578125" customWidth="1" style="7" min="5" max="5"/>
-    <col width="20.7109375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="25.7109375" customWidth="1" style="7" min="7" max="7"/>
-    <col width="17.28515625" customWidth="1" style="7" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="7" min="9" max="16384"/>
+    <col width="15.140625" customWidth="1" style="29" min="1" max="1"/>
+    <col width="44.5703125" customWidth="1" style="29" min="2" max="2"/>
+    <col width="35.85546875" customWidth="1" style="29" min="3" max="3"/>
+    <col width="11.7109375" customWidth="1" style="29" min="4" max="4"/>
+    <col width="9.42578125" customWidth="1" style="29" min="5" max="5"/>
+    <col width="20.7109375" customWidth="1" style="29" min="6" max="6"/>
+    <col width="25.7109375" customWidth="1" style="29" min="7" max="7"/>
+    <col width="17.28515625" customWidth="1" style="29" min="8" max="8"/>
+    <col width="9.140625" customWidth="1" style="29" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" style="29" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -778,7 +776,7 @@
       <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>订单</t>
         </is>
@@ -900,49 +898,49 @@
       </c>
       <c r="H6" s="20" t="n"/>
     </row>
-    <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="29" t="inlineStr">
+    <row r="7" ht="99.95" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2EC-Pink</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>细针洗头刷TPEE，硬度55，注意控制针头毛边，顶部印白色logo，颜色699C粉色，一盒两只</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F7" s="29">
+      <c r="E7" s="27" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F7" s="27">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr"/>
+      <c r="G7" s="27" t="n"/>
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1047,12 +1045,12 @@
           <t>箱规:</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr"/>
+      <c r="B15" s="25" t="n"/>
       <c r="C15" s="25" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="25" t="inlineStr"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
       <c r="H15" s="25" t="n"/>
     </row>
     <row r="16" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1069,8 +1067,8 @@
       <c r="C16" s="25" t="n"/>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="inlineStr"/>
-      <c r="G16" s="25" t="inlineStr"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
       <c r="H16" s="25" t="n"/>
     </row>
     <row r="17" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1087,8 +1085,8 @@
       <c r="C17" s="25" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="inlineStr"/>
-      <c r="G17" s="25" t="inlineStr"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
       <c r="H17" s="25" t="n"/>
     </row>
     <row r="18" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1101,8 +1099,8 @@
       <c r="C18" s="25" t="n"/>
       <c r="D18" s="25" t="n"/>
       <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="inlineStr"/>
-      <c r="G18" s="25" t="inlineStr"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
@@ -1136,7 +1134,7 @@
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>3）硬度按照55</t>
+          <t>3）硬度按照55(伟氏硬度计D型测值65+-0.8)(伟氏硬度计D型测值65+-0.8)</t>
         </is>
       </c>
       <c r="B21" s="25" t="n"/>
@@ -1206,7 +1204,7 @@
       <c r="I25" s="5" t="n"/>
     </row>
     <row r="26" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A26" s="25" t="inlineStr"/>
+      <c r="A26" s="25" t="n"/>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="25" t="n"/>
       <c r="D26" s="25" t="n"/>
@@ -1216,7 +1214,7 @@
       <c r="H26" s="25" t="n"/>
     </row>
     <row r="27" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A27" s="25" t="inlineStr"/>
+      <c r="A27" s="25" t="n"/>
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="25" t="n"/>
       <c r="D27" s="25" t="n"/>
@@ -1226,7 +1224,7 @@
       <c r="H27" s="25" t="n"/>
     </row>
     <row r="28" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A28" s="25" t="inlineStr"/>
+      <c r="A28" s="25" t="n"/>
       <c r="B28" s="25" t="n"/>
       <c r="C28" s="25" t="n"/>
       <c r="D28" s="25" t="n"/>
@@ -1236,7 +1234,7 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A29" s="25" t="inlineStr"/>
+      <c r="A29" s="25" t="n"/>
       <c r="B29" s="25" t="n"/>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="25" t="n"/>
@@ -1246,7 +1244,7 @@
       <c r="H29" s="25" t="n"/>
     </row>
     <row r="30" ht="17.25" customFormat="1" customHeight="1" s="5">
-      <c r="A30" s="25" t="inlineStr"/>
+      <c r="A30" s="25" t="n"/>
       <c r="B30" s="25" t="n"/>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="25" t="n"/>
